--- a/_journal_list.xlsx
+++ b/_journal_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SyncData\paper2_main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{486BFCDE-2A10-46F8-AA8E-8D0FD488784B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{908DC361-F1CB-4F18-BB11-3B2001519AAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="17010" yWindow="285" windowWidth="28110" windowHeight="16035" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$2:$I$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$2:$J$29</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="123">
   <si>
     <t>Note</t>
   </si>
@@ -175,18 +175,12 @@
     <t>Computational Visual Media</t>
   </si>
   <si>
-    <t xml:space="preserve">TSINGHUA UNIV PRESS </t>
-  </si>
-  <si>
     <t>https://cg.cs.tsinghua.edu.cn/cvmj/</t>
   </si>
   <si>
     <t>Applied Artificial Intelligence</t>
   </si>
   <si>
-    <t xml:space="preserve">TAYLOR &amp; FRANCIS INC </t>
-  </si>
-  <si>
     <t>https://www.tandfonline.com/journals/uaai20</t>
   </si>
   <si>
@@ -226,9 +220,6 @@
     <t>https://spj.science.org/journal/icomputing</t>
   </si>
   <si>
-    <t xml:space="preserve">AMER ASSOC ADVANCEMENT SCIENCE </t>
-  </si>
-  <si>
     <t>Journal Name</t>
   </si>
   <si>
@@ -283,17 +274,142 @@
     <t>https://link.springer.com/journal/10846</t>
   </si>
   <si>
-    <t xml:space="preserve"> Complex &amp; Intelligent Systems
-Publishing model</t>
-  </si>
-  <si>
     <t>https://link.springer.com/journal/40747</t>
   </si>
   <si>
-    <t>Review time</t>
-  </si>
-  <si>
-    <t>APC $</t>
+    <t>Acceptance Rate %</t>
+  </si>
+  <si>
+    <t>publication model (subscription or hybrid or open-acess)</t>
+  </si>
+  <si>
+    <t>APC $ (if hybrid or open-access)</t>
+  </si>
+  <si>
+    <t>4010 usd</t>
+  </si>
+  <si>
+    <t>open-access</t>
+  </si>
+  <si>
+    <t>hybrid</t>
+  </si>
+  <si>
+    <t>15 months</t>
+  </si>
+  <si>
+    <t>3560 usd</t>
+  </si>
+  <si>
+    <t>3290 usd</t>
+  </si>
+  <si>
+    <t>Tsinghua University Press</t>
+  </si>
+  <si>
+    <t>Taylor &amp; Francis</t>
+  </si>
+  <si>
+    <t>American Association for the Advancement of Science (AAAS)</t>
+  </si>
+  <si>
+    <t>3 months</t>
+  </si>
+  <si>
+    <t>0 usd</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>2330 usd</t>
+  </si>
+  <si>
+    <t>4 months</t>
+  </si>
+  <si>
+    <t>2720 usd</t>
+  </si>
+  <si>
+    <t>Avg Review time (from submission to acceptance)</t>
+  </si>
+  <si>
+    <t>5 months</t>
+  </si>
+  <si>
+    <t>8 months</t>
+  </si>
+  <si>
+    <t>3040 usd</t>
+  </si>
+  <si>
+    <t>3490 usd</t>
+  </si>
+  <si>
+    <t>6 months</t>
+  </si>
+  <si>
+    <t>3810 usd</t>
+  </si>
+  <si>
+    <t>1550 usd</t>
+  </si>
+  <si>
+    <t>2160 usd</t>
+  </si>
+  <si>
+    <t>2800 usd</t>
+  </si>
+  <si>
+    <t>short</t>
+  </si>
+  <si>
+    <t>hybird</t>
+  </si>
+  <si>
+    <t>7 months</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2240 usd</t>
+  </si>
+  <si>
+    <t>11 months</t>
+  </si>
+  <si>
+    <t>8.5 months</t>
+  </si>
+  <si>
+    <t>2970  usd</t>
+  </si>
+  <si>
+    <t>2890 usd</t>
+  </si>
+  <si>
+    <t>3390 usd</t>
+  </si>
+  <si>
+    <t>3350 usd</t>
+  </si>
+  <si>
+    <t>3590 usd</t>
+  </si>
+  <si>
+    <t>2930 usd</t>
+  </si>
+  <si>
+    <t>2380 usd</t>
+  </si>
+  <si>
+    <t>2850 usd</t>
+  </si>
+  <si>
+    <t>3190 usd</t>
+  </si>
+  <si>
+    <t>4.5 months</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Complex &amp; Intelligent Systems</t>
   </si>
 </sst>
 </file>
@@ -303,7 +419,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -329,6 +445,13 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -372,11 +495,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -402,10 +526,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -683,7 +813,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:I34"/>
+  <dimension ref="B1:K34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -692,12 +822,14 @@
     <col min="4" max="4" width="45.140625" style="1" customWidth="1"/>
     <col min="5" max="5" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="7" style="1" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="1"/>
+    <col min="7" max="7" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="38.7109375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="25.7109375" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C1" s="8"/>
       <c r="D1" s="8"/>
       <c r="E1" s="8"/>
@@ -705,10 +837,11 @@
       <c r="G1" s="8"/>
       <c r="H1" s="8"/>
       <c r="I1" s="8"/>
-    </row>
-    <row r="2" spans="2:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="J1" s="8"/>
+    </row>
+    <row r="2" spans="2:11" ht="45" x14ac:dyDescent="0.25">
       <c r="B2" s="3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>5</v>
@@ -723,16 +856,22 @@
         <v>32</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="I2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:11" ht="30" x14ac:dyDescent="0.25">
       <c r="B3" s="7" t="s">
         <v>36</v>
       </c>
@@ -748,19 +887,29 @@
       <c r="F3" s="6">
         <v>6.7</v>
       </c>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="4"/>
-    </row>
-    <row r="4" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="G3" s="9">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="K3" s="2"/>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B4" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>46</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>48</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>21</v>
@@ -768,13 +917,23 @@
       <c r="F4" s="6">
         <v>4</v>
       </c>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="4"/>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="G4" s="9">
+        <v>0.05</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="K4" s="2"/>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B5" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>6</v>
@@ -788,19 +947,29 @@
       <c r="F5" s="6">
         <v>3.5</v>
       </c>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="4"/>
-    </row>
-    <row r="6" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="G5" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="K5" s="2"/>
+    </row>
+    <row r="6" spans="2:11" ht="30" x14ac:dyDescent="0.25">
       <c r="B6" s="7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>22</v>
@@ -808,19 +977,29 @@
       <c r="F6" s="6">
         <v>7.8</v>
       </c>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="4"/>
-    </row>
-    <row r="7" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="G6" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="K6" s="2"/>
+    </row>
+    <row r="7" spans="2:11" ht="45" x14ac:dyDescent="0.25">
       <c r="B7" s="7" t="s">
         <v>43</v>
       </c>
       <c r="C7" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>44</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>45</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>22</v>
@@ -828,13 +1007,23 @@
       <c r="F7" s="6">
         <v>8.3000000000000007</v>
       </c>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="4"/>
-    </row>
-    <row r="8" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="G7" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="K7" s="2"/>
+    </row>
+    <row r="8" spans="2:11" ht="30" x14ac:dyDescent="0.25">
       <c r="B8" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>10</v>
@@ -848,19 +1037,29 @@
       <c r="F8" s="6">
         <v>3.6</v>
       </c>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="4"/>
-    </row>
-    <row r="9" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="G8" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="K8" s="2"/>
+    </row>
+    <row r="9" spans="2:11" ht="30" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>21</v>
@@ -868,11 +1067,21 @@
       <c r="F9" s="6">
         <v>3.4</v>
       </c>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="4"/>
-    </row>
-    <row r="10" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="G9" s="9">
+        <v>0.17</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="K9" s="2"/>
+    </row>
+    <row r="10" spans="2:11" ht="30" x14ac:dyDescent="0.25">
       <c r="B10" s="7" t="s">
         <v>3</v>
       </c>
@@ -888,13 +1097,23 @@
       <c r="F10" s="6">
         <v>9</v>
       </c>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="4"/>
-    </row>
-    <row r="11" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="G10" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="K10" s="2"/>
+    </row>
+    <row r="11" spans="2:11" ht="30" x14ac:dyDescent="0.25">
       <c r="B11" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>10</v>
@@ -908,19 +1127,29 @@
       <c r="F11" s="6">
         <v>9.4</v>
       </c>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="4"/>
-    </row>
-    <row r="12" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="G11" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="K11" s="2"/>
+    </row>
+    <row r="12" spans="2:11" ht="30" x14ac:dyDescent="0.25">
       <c r="B12" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>21</v>
@@ -928,19 +1157,29 @@
       <c r="F12" s="6">
         <v>3.8</v>
       </c>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="4"/>
-    </row>
-    <row r="13" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="G12" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="K12" s="2"/>
+    </row>
+    <row r="13" spans="2:11" ht="30" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>21</v>
@@ -948,13 +1187,23 @@
       <c r="F13" s="6">
         <v>4.5999999999999996</v>
       </c>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="4"/>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="G13" s="9">
+        <v>0.27</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="K13" s="2"/>
+    </row>
+    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B14" s="7" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>9</v>
@@ -968,19 +1217,29 @@
       <c r="F14" s="6">
         <v>3.6</v>
       </c>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="4"/>
-    </row>
-    <row r="15" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="G14" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="K14" s="2"/>
+    </row>
+    <row r="15" spans="2:11" ht="30" x14ac:dyDescent="0.25">
       <c r="B15" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>21</v>
@@ -988,13 +1247,23 @@
       <c r="F15" s="6">
         <v>4.5</v>
       </c>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="4"/>
-    </row>
-    <row r="16" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="G15" s="9">
+        <v>0.15</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="K15" s="2"/>
+    </row>
+    <row r="16" spans="2:11" ht="30" x14ac:dyDescent="0.25">
       <c r="B16" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>9</v>
@@ -1008,11 +1277,23 @@
       <c r="F16" s="6">
         <v>3.6</v>
       </c>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="4"/>
-    </row>
-    <row r="17" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="G16" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" ht="30" x14ac:dyDescent="0.25">
       <c r="B17" s="7" t="s">
         <v>14</v>
       </c>
@@ -1028,13 +1309,23 @@
       <c r="F17" s="6">
         <v>9.8000000000000007</v>
       </c>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="4"/>
-    </row>
-    <row r="18" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="G17" s="9">
+        <v>0.15</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="K17" s="2"/>
+    </row>
+    <row r="18" spans="2:11" ht="30" x14ac:dyDescent="0.25">
       <c r="B18" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>9</v>
@@ -1048,11 +1339,21 @@
       <c r="F18" s="6">
         <v>9.9</v>
       </c>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="4"/>
-    </row>
-    <row r="19" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="G18" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="K18" s="2"/>
+    </row>
+    <row r="19" spans="2:11" ht="30" x14ac:dyDescent="0.25">
       <c r="B19" s="7" t="s">
         <v>39</v>
       </c>
@@ -1068,13 +1369,23 @@
       <c r="F19" s="6">
         <v>2.4</v>
       </c>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="4"/>
-    </row>
-    <row r="20" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="G19" s="9">
+        <v>0.3</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="K19" s="2"/>
+    </row>
+    <row r="20" spans="2:11" ht="30" x14ac:dyDescent="0.25">
       <c r="B20" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>10</v>
@@ -1088,19 +1399,29 @@
       <c r="F20" s="6">
         <v>5</v>
       </c>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="4"/>
-    </row>
-    <row r="21" spans="2:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="G20" s="9">
+        <v>0.15</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="K20" s="2"/>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B21" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>61</v>
+        <v>57</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>89</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>22</v>
@@ -1108,19 +1429,29 @@
       <c r="F21" s="6">
         <v>6.4</v>
       </c>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="4"/>
-    </row>
-    <row r="22" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="G21" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="K21" s="2"/>
+    </row>
+    <row r="22" spans="2:11" ht="30" x14ac:dyDescent="0.25">
       <c r="B22" s="7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>21</v>
@@ -1128,19 +1459,29 @@
       <c r="F22" s="6">
         <v>4.8</v>
       </c>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="4"/>
-    </row>
-    <row r="23" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="G22" s="9">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="K22" s="2"/>
+    </row>
+    <row r="23" spans="2:11" ht="30" x14ac:dyDescent="0.25">
       <c r="B23" s="7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>21</v>
@@ -1148,13 +1489,23 @@
       <c r="F23" s="6">
         <v>3.5</v>
       </c>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="4"/>
-    </row>
-    <row r="24" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="G23" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="K23" s="2"/>
+    </row>
+    <row r="24" spans="2:11" ht="30" x14ac:dyDescent="0.25">
       <c r="B24" s="7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>6</v>
@@ -1168,11 +1519,21 @@
       <c r="F24" s="6">
         <v>4.9000000000000004</v>
       </c>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="4"/>
-    </row>
-    <row r="25" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="G24" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="K24" s="2"/>
+    </row>
+    <row r="25" spans="2:11" ht="30" x14ac:dyDescent="0.25">
       <c r="B25" s="7" t="s">
         <v>41</v>
       </c>
@@ -1188,11 +1549,21 @@
       <c r="F25" s="6">
         <v>8</v>
       </c>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="4"/>
-    </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="G25" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="K25" s="2"/>
+    </row>
+    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B26" s="7" t="s">
         <v>30</v>
       </c>
@@ -1208,13 +1579,23 @@
       <c r="F26" s="6">
         <v>2</v>
       </c>
-      <c r="G26" s="6"/>
-      <c r="H26" s="6"/>
-      <c r="I26" s="4"/>
-    </row>
-    <row r="27" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="G26" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="K26" s="2"/>
+    </row>
+    <row r="27" spans="2:11" ht="30" x14ac:dyDescent="0.25">
       <c r="B27" s="7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>10</v>
@@ -1228,11 +1609,21 @@
       <c r="F27" s="6">
         <v>6.7</v>
       </c>
-      <c r="G27" s="6"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="4"/>
-    </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="G27" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="K27" s="2"/>
+    </row>
+    <row r="28" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B28" s="7" t="s">
         <v>28</v>
       </c>
@@ -1248,11 +1639,21 @@
       <c r="F28" s="6">
         <v>2.6</v>
       </c>
-      <c r="G28" s="6"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="4"/>
-    </row>
-    <row r="29" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="G28" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="K28" s="2"/>
+    </row>
+    <row r="29" spans="2:11" ht="30" x14ac:dyDescent="0.25">
       <c r="B29" s="7" t="s">
         <v>26</v>
       </c>
@@ -1268,11 +1669,21 @@
       <c r="F29" s="6">
         <v>3.5</v>
       </c>
-      <c r="G29" s="6"/>
-      <c r="H29" s="6"/>
-      <c r="I29" s="4"/>
-    </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="G29" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="K29" s="2"/>
+    </row>
+    <row r="30" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B30" s="7" t="s">
         <v>33</v>
       </c>
@@ -1288,11 +1699,21 @@
       <c r="F30" s="6">
         <v>4.9000000000000004</v>
       </c>
-      <c r="G30" s="6"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="4"/>
-    </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="G30" s="9">
+        <v>0.3</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="J30" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="K30" s="2"/>
+    </row>
+    <row r="31" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B31" s="7" t="s">
         <v>4</v>
       </c>
@@ -1308,19 +1729,29 @@
       <c r="F31" s="6">
         <v>2.7</v>
       </c>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="4"/>
-    </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="G31" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="J31" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="K31" s="2"/>
+    </row>
+    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B32" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>21</v>
@@ -1328,19 +1759,29 @@
       <c r="F32" s="6">
         <v>3.4</v>
       </c>
-      <c r="G32" s="6"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="4"/>
-    </row>
-    <row r="33" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="G32" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="J32" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="K32" s="2"/>
+    </row>
+    <row r="33" spans="2:11" ht="30" x14ac:dyDescent="0.25">
       <c r="B33" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E33" s="4" t="s">
         <v>23</v>
@@ -1348,19 +1789,29 @@
       <c r="F33" s="6">
         <v>3.1</v>
       </c>
-      <c r="G33" s="6"/>
-      <c r="H33" s="6"/>
-      <c r="I33" s="4"/>
-    </row>
-    <row r="34" spans="2:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="G33" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="K33" s="2"/>
+    </row>
+    <row r="34" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B34" s="2" t="s">
-        <v>80</v>
+        <v>122</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>21</v>
@@ -1368,13 +1819,19 @@
       <c r="F34" s="6">
         <v>4.5</v>
       </c>
-      <c r="G34" s="6"/>
-      <c r="H34" s="6"/>
-      <c r="I34" s="4"/>
+      <c r="G34" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="I34" s="6"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="B2:I29" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:I32">
+  <autoFilter ref="B2:J29" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:J32">
     <sortCondition ref="B3:B32"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
